--- a/AAII_Financials/Yearly/FIG_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/FIG_YR_FIN.xlsx
@@ -1237,7 +1237,7 @@
         <v>-732100</v>
       </c>
       <c r="F27" s="3">
-        <v>285900</v>
+        <v>737800</v>
       </c>
       <c r="G27" s="3" t="s">
         <v>3</v>
@@ -1417,7 +1417,7 @@
         <v>-732100</v>
       </c>
       <c r="F33" s="3">
-        <v>285900</v>
+        <v>737800</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>3</v>
@@ -1477,7 +1477,7 @@
         <v>-732100</v>
       </c>
       <c r="F35" s="3">
-        <v>285900</v>
+        <v>737800</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>3</v>
@@ -2667,7 +2667,7 @@
         <v>-732100</v>
       </c>
       <c r="F81" s="3">
-        <v>285900</v>
+        <v>737800</v>
       </c>
       <c r="G81" s="3" t="s">
         <v>3</v>
